--- a/ITG_Richmond_Green_Yellow_HubSpot_Import.xlsx
+++ b/ITG_Richmond_Green_Yellow_HubSpot_Import.xlsx
@@ -380,7 +380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -394,6 +394,7 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -452,6 +453,11 @@
           <t>Phone number</t>
         </is>
       </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>Address source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -504,7 +510,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -562,6 +572,11 @@
           <t>804-673-2722</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -589,6 +604,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7130 Glen Forest Drive, Suite 101</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>23226</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>804-288-4084</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -616,6 +666,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8700 Stony Point Parkway, Suite 120</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>23235</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>804-323-5011</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -643,6 +728,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>7202 Glen Forest Drive, Suite 200</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Henrico</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>23226</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>804-673-2024</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -670,6 +790,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>9101 Stony Point Drive</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>23235</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>804-330-9105</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -697,6 +852,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>6600 West Broad Street, Suite 300</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>804-320-4243</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -754,6 +944,11 @@
           <t>804-282-4205</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -811,6 +1006,11 @@
           <t>804-320-7139</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -868,6 +1068,11 @@
           <t>804-285-2006</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -925,6 +1130,11 @@
           <t>804-288-8204</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -982,6 +1192,11 @@
           <t>804-288-1953</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -1039,6 +1254,11 @@
           <t>(804) 897-2100</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -1066,6 +1286,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>400 Westhampton Station</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>23226</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>804-287-2020</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -1093,6 +1348,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>7110 Forest Ave, Suite 203</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>23226</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>804-442-3558</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -1145,7 +1435,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -1173,6 +1467,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>12390 Three Chopt Road</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>23233</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>804-351-5432</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -1225,7 +1554,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -1278,7 +1611,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -1306,6 +1643,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>200 North 22nd Street</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>23223</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>804-644-9590</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -1333,6 +1705,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>5511 Staples Mill Road, Suite 102</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>23228</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>804-440-3700</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -1360,6 +1767,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1010 N Thompson St</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>804-358-6343</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -1387,6 +1829,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>517 W. Grace Street</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>23220</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>804-783-2505</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -1414,6 +1891,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>4905 Dickels Road, Suite 106</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>804-712-4133</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -1441,6 +1953,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1101 Hampton St</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>23220</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>804-359-4093</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -1468,6 +2015,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>4825 South Laburnum Avenue</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>23231</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>804-328-1784</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -1495,6 +2077,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1000 Boulders Parkway, Suite 202</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>23225</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>804-320-7881</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -1552,6 +2169,11 @@
           <t>804-592-6311</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -1609,6 +2231,11 @@
           <t>804-233-5481</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -1636,6 +2263,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>5111 Old Midlothian Tpke</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>23224</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>804-732-9253</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -1663,6 +2325,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>5004 Monument Ave</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>804-358-1150</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -1690,6 +2387,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2924 Emerywood Parkway, Suite 300</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>23294</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>800-746-6768</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -1717,6 +2449,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>5516 Falmouth Street, Suite 302</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>804-377-3590</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -1769,7 +2536,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -1822,7 +2593,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -1880,6 +2655,11 @@
           <t>(804) 292-2366</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -1907,6 +2687,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2369 Staples Mill Road, Suite 200</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>804-285-8206</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -1934,6 +2749,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1115 Boulders Parkway, Suite 100</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>23225</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>804-320-1339</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -1991,6 +2841,11 @@
           <t>804-288-7901</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -2018,6 +2873,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>6372 Mechanicsville Turnpike, Suite 103</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Mechanicsville</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>23111</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>804-379-0116</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -2070,7 +2960,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -2098,6 +2992,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1011 Hioaks Rd</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>23225</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>804-523-4634</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -2155,6 +3084,11 @@
           <t>804-381-6252</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -2182,6 +3116,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>7650 East Parham Road, MOB II Suite 210</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>23294</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>804-272-2702</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -2234,7 +3203,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -2287,7 +3260,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -2315,6 +3292,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>204 N. Hamilton Street, Suite B</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>23221</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>877-773-3869</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -2342,6 +3354,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>4900 West Marshall Street</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>804-355-5717</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -2369,6 +3416,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1700 Willow Lawn Drive, Suite 210</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>804-282-9999</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -2396,6 +3478,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2125 Hilliard Road</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>23228</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>804-266-9666</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
@@ -2423,6 +3540,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2125 Hilliard Road</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>23228</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>804-201-4251</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -2480,6 +3632,11 @@
           <t>804-299-3155</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -2507,6 +3664,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>605 Research Rd, Suite C</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>23236</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>804-402-4420</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
@@ -2564,6 +3756,11 @@
           <t>804-622-5852</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -2621,6 +3818,11 @@
           <t>804-421-9326</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -2673,7 +3875,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
@@ -2731,6 +3937,11 @@
           <t>804-276-2800</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -2783,7 +3994,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
@@ -2836,7 +4051,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
@@ -2889,7 +4108,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
@@ -2942,7 +4165,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -2970,6 +4197,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>14653 Mountain Rd</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Glen Allen</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>23059</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>804-205-0379</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
@@ -3022,7 +4284,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
@@ -3080,6 +4346,11 @@
           <t>804-410-3300</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
@@ -3132,7 +4403,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
@@ -3160,6 +4435,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>9520 Bird Dog Dr</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Mechanicsville</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>23116</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>804-559-5417</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
@@ -3217,6 +4527,11 @@
           <t>804-594-6667</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
@@ -3269,7 +4584,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -3327,6 +4646,11 @@
           <t>804-798-1477</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -3379,7 +4703,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
@@ -3432,7 +4760,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
@@ -3490,6 +4822,11 @@
           <t>804-328-0444</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
@@ -3542,7 +4879,11 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
@@ -3600,6 +4941,11 @@
           <t>(804) 423-8372</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
@@ -3627,6 +4973,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>4915 Fitzhugh Avenue</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>804-562-5777</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -3654,6 +5035,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>7001 Forest Avenue, Suite 300</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>804-420-1212</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -3681,6 +5097,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>7605 Forest Ave, Suite 211</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>23229</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>804-282-3114</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
@@ -3708,6 +5159,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>PO Box 13526</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>23225</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>804-276-9364</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
@@ -3735,6 +5221,41 @@
           <t>https://github.com/psdwizzard/Lists</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2810 North Parham Road, Suite 120</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>23294</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>804-288-1881</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -3760,6 +5281,41 @@
       <c r="E81" s="7" t="inlineStr">
         <is>
           <t>https://github.com/psdwizzard/Lists</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>9221 Forest Hill Avenue</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>23235</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>804-355-0300</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Web research</t>
         </is>
       </c>
     </row>
@@ -3876,7 +5432,6 @@
           <t>23226</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4586,7 +6141,6 @@
           <t>23294</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4624,7 +6178,6 @@
           <t>23230</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4662,7 +6215,6 @@
           <t>23113</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4700,7 +6252,6 @@
           <t>23233</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4738,7 +6289,6 @@
           <t>23236</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4776,7 +6326,6 @@
           <t>23236</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4814,7 +6363,6 @@
           <t>23233</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4852,7 +6400,6 @@
           <t>23230</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4890,7 +6437,6 @@
           <t>23116</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4928,7 +6474,6 @@
           <t>23233</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4966,7 +6511,6 @@
           <t>23114</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5004,7 +6548,6 @@
           <t>23235</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5084,7 +6627,6 @@
           <t>23230</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5122,7 +6664,6 @@
           <t>23229</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5244,7 +6785,6 @@
           <t>23116</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5282,7 +6822,6 @@
           <t>23060</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5320,7 +6859,6 @@
           <t>23219</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5358,7 +6896,6 @@
           <t>23112</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5396,7 +6933,6 @@
           <t>23220</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5434,7 +6970,6 @@
           <t>23060</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5472,7 +7007,6 @@
           <t>23112</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5510,7 +7044,6 @@
           <t>23220</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5548,7 +7081,6 @@
           <t>23060</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5712,7 +7244,6 @@
           <t>23832</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5792,7 +7323,6 @@
           <t>23832</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5830,7 +7360,6 @@
           <t>23229</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5952,7 +7481,6 @@
           <t>23229</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5990,7 +7518,6 @@
           <t>23221</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6028,7 +7555,6 @@
           <t>23112</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6066,7 +7592,6 @@
           <t>22401</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6104,7 +7629,6 @@
           <t>23233</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6142,7 +7666,6 @@
           <t>23112</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6306,7 +7829,6 @@
           <t>23236</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6386,7 +7908,6 @@
           <t>23112</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6424,7 +7945,6 @@
           <t>23112</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6462,7 +7982,6 @@
           <t>23112</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6500,7 +8019,6 @@
           <t>23112</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6538,7 +8056,6 @@
           <t>23111</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6576,7 +8093,6 @@
           <t>23228</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6614,7 +8130,6 @@
           <t>23228</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6694,7 +8209,6 @@
           <t>23230</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6732,7 +8246,6 @@
           <t>23230</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6770,7 +8283,6 @@
           <t>23226</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6850,7 +8362,6 @@
           <t>23059</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6888,7 +8399,6 @@
           <t>23226</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7010,7 +8520,6 @@
           <t>23234</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7090,7 +8599,6 @@
           <t>23005</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7128,7 +8636,6 @@
           <t>23005</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7166,7 +8673,6 @@
           <t>23227</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7204,7 +8710,6 @@
           <t>23219</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7284,7 +8789,6 @@
           <t>23223</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7322,7 +8826,6 @@
           <t>23223</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7360,7 +8863,6 @@
           <t>23223</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7398,7 +8900,6 @@
           <t>23832</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7478,7 +8979,6 @@
           <t>23114</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ITG_Richmond_Green_Yellow_HubSpot_Import.xlsx
+++ b/ITG_Richmond_Green_Yellow_HubSpot_Import.xlsx
@@ -54,7 +54,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -71,6 +71,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -380,7 +383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -395,6 +398,7 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,6 +462,11 @@
           <t>Address source</t>
         </is>
       </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -639,6 +648,16 @@
           <t>Web research</t>
         </is>
       </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (5):
+• West End — 6600 West Broad Street, Suite 100, Richmond, VA 23230 (804-288-4084)
+• Short Pump — 12129 Graham Meadows Drive, Richmond, VA 23233 (804-288-4084)
+• Midlothian — 13801 St. Francis Boulevard, Suite 100, Midlothian, VA 23114 (804-288-4084)
+• Mechanicsville — 8364 Bell Creek Road, Mechanicsville, VA 23116 (804-288-4084)
+• Kilmarnock — 102 DMV Drive, Kilmarnock, VA 22482 (804-288-4084)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -701,6 +720,19 @@
           <t>Web research</t>
         </is>
       </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (8):
+• Mechanicsville / Bell Creek — 7515 Right Flank Road, Mechanicsville, VA 23116 (804-559-0405)
+• Midlothian on Hull — 6120 Harbourside Centre Loop, Midlothian, VA 23112 (804-915-1400)
+• Prince George / Waterside — 4700 Puddledock Road, Suite 400, Prince George, VA 23875 (804-458-1740)
+• Quinton / New Kent — 1850 Pocahontas Trail, Quinton, VA 23141 (804-559-0405)
+• Short Pump / West Creek — 1630 Wilkes Ridge Parkway, Suite 303, Richmond, VA 23233 (804-708-0445)
+• Tappahannock — 1396 Tappahannock Blvd, Unit B, Tappahannock, VA 22560 (804-288-4827)
+• Heart &amp; Vascular Surgery Center — 8007 Discovery Drive, Unit B, Richmond, VA 23229 (804-288-4827)
+• West End / Forest Medical Plaza — 7611 Forest Ave, Suite 100 &amp; 100A, Richmond, VA 23229 (804-288-4827)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -825,6 +857,18 @@
           <t>Web research</t>
         </is>
       </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (7):
+• Hanover / Mechanicsville — 8152 Pleasant Grove Road, Mechanicsville, VA 23116 (804-330-9105)
+• Reynolds Crossing — 6900 Forest Avenue, Suite 200, Richmond, VA 23230 (804-330-9105)
+• Far West End / Goochland — 1700 Mills Road, Suite B, Goochland, VA 23233 (804-330-9105)
+• IR Center — 1700 Mills Road, Suite A, Goochland, VA 23233 (804-773-4700)
+• Prince George — 2025 Waterside Road, Suite 105, Prince George, VA 23875 (804-330-9105)
+• Tappahannock — 1396 B Tappahannock Blvd, Tappahannock, VA 22560 (804-330-9105)
+• Emporia — 6 Doctor's Drive, Emporia, VA 23847 (804-330-9105)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -949,6 +993,13 @@
           <t>CSV export</t>
         </is>
       </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (2):
+• West End — 7240 Patterson Avenue, Suite 100, Richmond, VA 23229 (804-282-4205)
+• Mechanicsville — 8485 Bell Creek Road, Suite B3, Mechanicsville, VA 23116 (804-282-4205)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -1011,6 +1062,12 @@
           <t>CSV export</t>
         </is>
       </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (1):
+• Midlothian — 13470 Tredegar Lake Parkway, Midlothian, VA 23112 (804-794-7788)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1073,6 +1130,13 @@
           <t>CSV export</t>
         </is>
       </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (2):
+• Mechanicsville — 7498 Right Flank Road, Mechanicsville, VA 23116 (804-730-2652)
+• Bon Air — 10800 Midlothian Turnpike, Suite 309, Richmond, VA 23235 (804-794-2307)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1135,6 +1199,13 @@
           <t>CSV export</t>
         </is>
       </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (2):
+• Mechanicsville — 8407 North Run Medical Drive, Mechanicsville, VA 23116 (804-559-4880)
+• Bon Air — 1011 Johnston Willis Drive, Suite 100, North Chesterfield, VA 23235 (804-330-4990)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -1197,6 +1268,13 @@
           <t>CSV export</t>
         </is>
       </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (2):
+• Mechanicsville — 8237 Meadowbridge Road, Mechanicsville, VA 23116 (804-288-1953)
+• Midlothian — 13460 Tredegar Lake Parkway, Midlothian, VA 23112 (804-288-1953)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -1321,6 +1399,18 @@
           <t>Web research</t>
         </is>
       </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (7):
+• Short Pump — 12018 W. Broad St, Suite 100, Henrico, VA 23233 (804-287-2020)
+• Hanover — 8120 Pleasant Grove Rd, Suite 100, Mechanicsville, VA 23116 (804-287-2020)
+• Reynolds Crossing — 6946 Forest Avenue, Suite 100, Richmond, VA 23230 (804-287-2020)
+• Puddledock — 2015 Waterside Road, Prince George, VA 23875 (804-287-2020)
+• Ironbridge — 11601 Iron Bridge Road, Suite 104, Chester, VA 23831 (804-287-2020)
+• Westchester — 611 Watkins Centre Pkwy, Building 2, Midlothian, VA 23114 (804-287-2020)
+• The Aesthetic Center — 12018 W. Broad Street, Suite 102, Henrico, VA 23233 (804-287-2020)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -1440,6 +1530,14 @@
           <t>CSV export</t>
         </is>
       </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (3):
+• West End — 5001 Libbie Mill East Blvd. #125, Richmond, VA 23230
+• Unassigned — 14261 Winterview Parkway, Midlothian, VA 23113
+• Short Pump — 3400 Haydenpark Lane Suite 203, Henrico, VA 23233</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -1502,6 +1600,20 @@
           <t>Web research</t>
         </is>
       </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (9):
+• Atlee - Ashland — 9484 Charter Gate Drive, Ashland, VA 23005 (804-412-0599)
+• Brandermill - Woodlake — 6510 Harbour View Court, Midlothian, VA 23112 (804-739-6494)
+• Chester — 2601 Swiftrun Road, Chester, VA 23831 (804-414-2550)
+• Huguenot Specialty Center — 1801 Huguenot Road, Midlothian, VA 23113 (804-419-1041)
+• Ironbridge - Courthouse — 6441 Ironbridge Road, Richmond, VA 23234 (804-743-8189)
+• Mechanicsville Specialty Center — 6000 Brashier Blvd, Mechanicsville, VA 23111 (804-730-3457)
+• Midlothian - 288 — 14001 Charter Park Drive, Midlothian, VA 23114 (804-417-0245)
+• Powhatan — 2625 Anderson Highway, Powhatan, VA 23139 (804-403-6036)
+• Tri-Cities — 4710 Puddledock Road, Prince George, VA 23875 (804-526-4886)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -1559,6 +1671,17 @@
           <t>CSV export</t>
         </is>
       </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (6):
+• Unassigned — 223 Wadsworth Drive, N. Chesterfield, VA 23236
+• Short Pump — 1600 Wilkes Ridge Drive Suite 200, Henrico, VA 23233
+• West End — 2369 Staples Mill Road Suite 100, Richmond, VA 23230
+• Mechanicsville — 8415 North Run Medical Drive, Mechanicsville, VA 23116
+• Short Pump — 1600 Wilkes Ridge Drive Suite 100, Henrico, VA 23233
+• Unassigned — 15350 East West Road Suite 101, Midlothian, VA 23114</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -1740,6 +1863,12 @@
           <t>Web research</t>
         </is>
       </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (1):
+• Roanoke HQ — 5673 Airport Road, Roanoke, VA 24012 (540-344-7700)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -1864,6 +1993,16 @@
           <t>Web research</t>
         </is>
       </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (5):
+• Health Services — 511 W. Grace Street, Richmond, VA 23220 (804-783-2505)
+• Southside Health Center — 180 E. Belt Boulevard, Richmond, VA 23224 (804-783-2505)
+• East Cary Health Center — 24 E. Cary Street, Richmond, VA 23219 (804-783-2505)
+• Medical Respite — 180 Belt Boulevard, Richmond, VA 23224 (804-292-3030)
+• Safe Haven — 2864 Hull Street, Richmond, VA 23224 (804-231-7137)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -2174,6 +2313,13 @@
           <t>CSV export</t>
         </is>
       </c>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (2):
+• West End — 1900 Byrd Ave, Richmond, VA 23230
+• West End — 8804 Patterson Ave, Richmond, VA 23229</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -2236,6 +2382,12 @@
           <t>CSV export</t>
         </is>
       </c>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (1):
+• Midlothian — 12910 Genito Road, Midlothian, VA 23112 (804-744-0716)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -2541,6 +2693,13 @@
           <t>CSV export</t>
         </is>
       </c>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (2):
+• Glen Allen — 4101 Cox Road, Suite 360 Glen Allen, VA 23060
+• Downtown — 407 East Canal Street, Richmond, VA 23219</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -2598,6 +2757,16 @@
           <t>CSV export</t>
         </is>
       </c>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (5):
+• Richmond city — verify neighborhood — 1127 W Main St, Richmond, VA 23220
+• Glen Allen — 2400 Old Brick Rd, #178, Glen Allen, VA 23060
+• Midlothian — 2913 Fox Chase Lane, Midlothian, VA 23112
+• Richmond city — verify neighborhood — 1127 W Main St, Richmond, VA 23220
+• Glen Allen — 2400 Old Brick Rd, Glen Allen, VA 23060</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -2784,6 +2953,17 @@
           <t>Web research</t>
         </is>
       </c>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (6):
+• Henrico Parham — 7650 East Parham Road, Suite 100, Richmond, VA 23294 (804-288-3136)
+• Shrader Road — 7858 Shrader Road, Richmond, VA 23294 (804-270-1305)
+• St. Mary's — 5899 Bremo Road, Suite 100A, Richmond, VA 23226 (804-288-8512)
+• Westchester — 15300 East West Road, Midlothian, VA 23114 (804-379-2414)
+• Westchester Ortho On Call — 15564 Westchester Commons Way, Midlothian, VA 23113 (804-440-4878)
+• Hull St — 13212 Hull St. Rd, Midlothian, VA 23112 (804-419-9840)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -2846,6 +3026,12 @@
           <t>CSV export</t>
         </is>
       </c>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (1):
+• West End — 7702 E. Parham Rd., Suite 101, Richmond, VA 23294 (804-288-7901)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -2908,6 +3094,12 @@
           <t>Web research</t>
         </is>
       </c>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (1):
+• Midlothian — 1316 Alverser Plaza, Midlothian, VA 23113 (804-379-0116)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -2965,6 +3157,13 @@
           <t>CSV export</t>
         </is>
       </c>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (2):
+• Unassigned — 7300 Ashlake Parkway, Suite 200 Chesterfield, VA 23832
+• West End — 8006 Discovery Drive, Suite 400 Henrico, VA 23229</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -3027,6 +3226,12 @@
           <t>Web research</t>
         </is>
       </c>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (1):
+• West End / Glen Allen — 3920 Springfield Rd, Glen Allen, VA 23060 (804-747-7472)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -3089,6 +3294,12 @@
           <t>CSV export</t>
         </is>
       </c>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (1):
+• West End — 7605 Forest Avenue, Suite 412, Richmond, VA 23229 (804-381-6252)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -3265,6 +3476,15 @@
           <t>CSV export</t>
         </is>
       </c>
+      <c r="M47" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (4):
+• Unassigned — 12077 Hull Street Rd, Midlothian, VA 23112
+• Unassigned — 1301 Central Park Blvd, Fredericksburg, VA 22401
+• Short Pump — 4300 Greybull Drive, Henrico, VA 23233
+• Unassigned — 12077 Hull Street Road, Midlothian, VA 23112</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -4351,6 +4571,12 @@
           <t>CSV export</t>
         </is>
       </c>
+      <c r="M65" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (1):
+• Unassigned — 11207 Nuckols Rd Ste F, Glen Allen, VA 23059</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
@@ -4651,6 +4877,13 @@
           <t>CSV export</t>
         </is>
       </c>
+      <c r="M70" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (2):
+• Unassigned — 10448 Dow-Gil Rd, Ashland, VA 23005
+• Unassigned — 10448 Dow-Gil Rd, Ashland, VA 23005</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -4827,6 +5060,14 @@
           <t>CSV export</t>
         </is>
       </c>
+      <c r="M73" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (3):
+• Richmond city — verify neighborhood — 5207 Nine Mile Rd, Richmond, VA 23223
+• Richmond city — verify neighborhood — 5184 Nine Mile Rd, Richmond, VA 23223
+• Richmond city — verify neighborhood — 5168 Nine Mile Rd, Richmond, VA 23223</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
@@ -5316,6 +5557,12 @@
       <c r="L81" t="inlineStr">
         <is>
           <t>Web research</t>
+        </is>
+      </c>
+      <c r="M81" s="10" t="inlineStr">
+        <is>
+          <t>Additional locations (1):
+• FACT Autism Resource Center — 3509 Virginia Beach Boulevard, Virginia Beach, VA 23452 (804-355-0300)</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -5399,12 +5646,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Commonwealth Primary Care</t>
+          <t>Advantage Primary Care</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>cpcva.com</t>
+          <t>advantagerva.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5414,7 +5661,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1800 Glenside Drive, Suite 101</t>
+          <t>7605 Forest Ave STE 412</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5429,19 +5676,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>23226</t>
+          <t>23229</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>804-381-6252</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Richmond Nephrology Associates</t>
+          <t>Advantage Primary Care</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>richmondnephrologyassociates.com</t>
+          <t>advantagerva.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5451,7 +5703,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7001 West Broad Street, Suite A</t>
+          <t>7605 Forest Avenue, Suite 412</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5466,39 +5718,39 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>23294</t>
+          <t>23229</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>804-673-2722</t>
+          <t>804-381-6252</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pediatric Associates of Richmond</t>
+          <t>AHG Construction &amp; Remodeling</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>parpeds.com</t>
+          <t>ahgva.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Short Pump</t>
+          <t>Mechanicsville</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4300 Pouncey Tract Road</t>
+          <t>9600 Atlee Station Road</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Glen Allen</t>
+          <t>Mechanicsville</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5508,24 +5760,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>23060</t>
+          <t>23116</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>804-282-4205</t>
+          <t>804-299-3155</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pediatric Associates of Richmond</t>
+          <t>A Plus Roofing Company - Richmond VA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>parpeds.com</t>
+          <t>aplusroofing.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5535,7 +5787,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7240 Patterson Avenue, Suite 100</t>
+          <t>2907 Hungary Spring Rd</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5550,39 +5802,35 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>23229</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>804-282-4205</t>
-        </is>
-      </c>
+          <t>23228</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pediatric Associates of Richmond</t>
+          <t>A Plus Roofing Company - Richmond VA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>parpeds.com</t>
+          <t>aplusroofing.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mechanicsville</t>
+          <t>West End</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8485 Bell Creek Road, Suite B3</t>
+          <t>2907 Hungary Spring Rd</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mechanicsville</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5592,34 +5840,30 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>23116</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>804-282-4205</t>
-        </is>
-      </c>
+          <t>23228</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pediatric Associates, PC</t>
+          <t>A Plus Roofing Company - Richmond VA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pediatricassociatespc.com</t>
+          <t>aplusroofing.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hioaks / Chippenham</t>
+          <t>West End</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1001 Hioaks Road</t>
+          <t>2907 Hungary Spring Rd</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5634,39 +5878,39 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>23225</t>
+          <t>23228</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>804-320-7139</t>
+          <t>(804) 752-0008</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pediatric Associates, PC</t>
+          <t>Blue and Gray Self-Storage</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pediatricassociatespc.com</t>
+          <t>blueandgraystorage.com</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13470 Tredegar Lake Parkway</t>
+          <t>15221 Hull Street Rd.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -5676,39 +5920,35 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>23112</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>804-794-7788</t>
-        </is>
-      </c>
+          <t>23832</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dermatology Associates of Virginia</t>
+          <t>Byrd Property Management</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dermva.com</t>
+          <t>byrdpm.com</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reynolds Crossing</t>
+          <t>Midlothian</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6946 Forest Avenue, Suite 200</t>
+          <t>2913 Fox Chase Ln</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Midlothian</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5718,39 +5958,35 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>23230</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>804-285-2006</t>
-        </is>
-      </c>
+          <t>23112</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dermatology Associates of Virginia</t>
+          <t>Byrd Property Management</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dermva.com</t>
+          <t>byrdpm.com</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mechanicsville</t>
+          <t>Richmond city — verify neighborhood</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7498 Right Flank Road</t>
+          <t>1127 W Main St</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mechanicsville</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5760,39 +5996,35 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>23116</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>804-730-2652</t>
-        </is>
-      </c>
+          <t>23220</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dermatology Associates of Virginia</t>
+          <t>Byrd Property Management</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>dermva.com</t>
+          <t>byrdpm.com</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bon Air</t>
+          <t>Glen Allen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10800 Midlothian Turnpike, Suite 309</t>
+          <t>2400 Old Brick Rd, #178</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Glen Allen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5802,39 +6034,35 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>23235</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>804-794-2307</t>
-        </is>
-      </c>
+          <t>23060</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Neurosurgical Associates</t>
+          <t>Byrd Property Management</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>neurosurgicalva.com</t>
+          <t>byrdpm.com</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Short Pump</t>
+          <t>Midlothian</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1600 Wilkes Ridge Road, Suite 210</t>
+          <t>2913 Fox Chase Lane</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Henrico</t>
+          <t>Midlothian</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -5844,39 +6072,35 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>23233</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>804-288-8204</t>
-        </is>
-      </c>
+          <t>23112</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Neurosurgical Associates</t>
+          <t>Byrd Property Management</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>neurosurgicalva.com</t>
+          <t>byrdpm.com</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mechanicsville</t>
+          <t>Richmond city — verify neighborhood</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8407 North Run Medical Drive</t>
+          <t>1127 W Main St</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mechanicsville</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -5886,39 +6110,35 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>23116</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>804-559-4880</t>
-        </is>
-      </c>
+          <t>23220</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Neurosurgical Associates</t>
+          <t>Byrd Property Management</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>neurosurgicalva.com</t>
+          <t>byrdpm.com</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bon Air</t>
+          <t>Glen Allen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1011 Johnston Willis Drive, Suite 100</t>
+          <t>2400 Old Brick Rd</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>North Chesterfield</t>
+          <t>Glen Allen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -5928,39 +6148,35 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>23235</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>804-330-4990</t>
-        </is>
-      </c>
+          <t>23060</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Vascular Surgery Associates</t>
+          <t>Center for Physical Therapy &amp; Sports Medicine</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>vascularsurgeryassociates.com</t>
+          <t>centerforpt.net</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>West End</t>
+          <t>Southside</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7900 Shrader Road</t>
+          <t>1011 Hioaks Rd</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Henrico</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5970,39 +6186,39 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>23294</t>
+          <t>23225</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>804-288-1953</t>
+          <t>804-523-4634</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Vascular Surgery Associates</t>
+          <t>Center for Physical Therapy &amp; Sports Medicine</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>vascularsurgeryassociates.com</t>
+          <t>centerforpt.net</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mechanicsville</t>
+          <t>West End / Glen Allen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8237 Meadowbridge Road</t>
+          <t>3920 Springfield Rd</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mechanicsville</t>
+          <t>Glen Allen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -6012,39 +6228,39 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>23116</t>
+          <t>23060</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>804-288-1953</t>
+          <t>804-747-7472</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Vascular Surgery Associates</t>
+          <t>Chesterfield Auto Parts</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>vascularsurgeryassociates.com</t>
+          <t>chesterfieldauto.com</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Southside / Midlothian corridor</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13460 Tredegar Lake Parkway</t>
+          <t>5111 Old Midlothian Turnpike</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -6054,34 +6270,34 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>23112</t>
+          <t>23224</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>804-288-1953</t>
+          <t>804-233-5481</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Virginia Physicians for Women</t>
+          <t>Chesterfield Auto Parts</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>vpfw.com</t>
+          <t>chesterfieldauto.com</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Midlothian</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13801 St. Francis Boulevard, Suite 150</t>
+          <t>12910 Genito Road</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -6096,34 +6312,34 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>23114</t>
+          <t>23112</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(804) 897-2100</t>
+          <t>804-744-0716</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>River Run Dental</t>
+          <t>Commonwealth Autism</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>riverrundentalspa.com</t>
+          <t>commonwealthautism.org</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>West End</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7820 Shrader Road</t>
+          <t>9221 Forest Hill Avenue</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -6138,34 +6354,39 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>23294</t>
+          <t>23235</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>804-355-0300</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>River Run Dental</t>
+          <t>Commonwealth Autism</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>riverrundentalspa.com</t>
+          <t>commonwealthautism.org</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>West End</t>
+          <t>FACT Autism Resource Center</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5001 Libbie Mill East Blvd. #125</t>
+          <t>3509 Virginia Beach Boulevard</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Virginia Beach</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -6175,34 +6396,39 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>23230</t>
+          <t>23452</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>804-355-0300</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>River Run Dental</t>
+          <t>Commonwealth Primary Care</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>riverrundentalspa.com</t>
+          <t>cpcva.com</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>West End</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>14261 Winterview Parkway</t>
+          <t>1800 Glenside Drive, Suite 101</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -6212,34 +6438,35 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>23113</t>
-        </is>
-      </c>
+          <t>23226</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>River Run Dental</t>
+          <t>Daily Planet Health Services</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>riverrundentalspa.com</t>
+          <t>dailyplanetva.org</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Short Pump</t>
+          <t>Administration / West Grace</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3400 Haydenpark Lane Suite 203</t>
+          <t>517 W. Grace Street</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Henrico</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -6249,34 +6476,39 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>23233</t>
+          <t>23220</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>804-783-2505</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Richmond Gastroenterology Associates</t>
+          <t>Daily Planet Health Services</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>richmondgastro.com</t>
+          <t>dailyplanetva.org</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Health Services</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>169 Wadsworth Drive</t>
+          <t>511 W. Grace Street</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>N. Chesterfield</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -6286,34 +6518,39 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>23236</t>
+          <t>23220</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>804-783-2505</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Richmond Gastroenterology Associates</t>
+          <t>Daily Planet Health Services</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>richmondgastro.com</t>
+          <t>dailyplanetva.org</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Southside Health Center</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>223 Wadsworth Drive</t>
+          <t>180 E. Belt Boulevard</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>N. Chesterfield</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -6323,34 +6560,39 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>23236</t>
+          <t>23224</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>804-783-2505</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Richmond Gastroenterology Associates</t>
+          <t>Daily Planet Health Services</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>richmondgastro.com</t>
+          <t>dailyplanetva.org</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Short Pump</t>
+          <t>East Cary Health Center</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1600 Wilkes Ridge Drive Suite 200</t>
+          <t>24 E. Cary Street</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Henrico</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -6360,29 +6602,34 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>23233</t>
+          <t>23219</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>804-783-2505</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Richmond Gastroenterology Associates</t>
+          <t>Daily Planet Health Services</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>richmondgastro.com</t>
+          <t>dailyplanetva.org</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>West End</t>
+          <t>Medical Respite</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2369 Staples Mill Road Suite 100</t>
+          <t>180 Belt Boulevard</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -6397,34 +6644,39 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>23230</t>
+          <t>23224</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>804-292-3030</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Richmond Gastroenterology Associates</t>
+          <t>Daily Planet Health Services</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>richmondgastro.com</t>
+          <t>dailyplanetva.org</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mechanicsville</t>
+          <t>Safe Haven</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8415 North Run Medical Drive</t>
+          <t>2864 Hull Street</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mechanicsville</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -6434,34 +6686,39 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>23116</t>
+          <t>23224</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>804-231-7137</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Richmond Gastroenterology Associates</t>
+          <t>Dallan Construction</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>richmondgastro.com</t>
+          <t>dallanconstruction.com</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Short Pump</t>
+          <t>West End</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1600 Wilkes Ridge Drive Suite 100</t>
+          <t>4900 Fitzhugh Avenue</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Henrico</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -6471,34 +6728,39 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>23233</t>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>804-421-9326</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Richmond Gastroenterology Associates</t>
+          <t>Dominion Behavioral Healthcare - Richmond</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>richmondgastro.com</t>
+          <t>dbhrichmond.com</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>West End</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>15350 East West Road Suite 101</t>
+          <t>2301 North Parham Rd</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Suite 5 Richmond</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -6508,29 +6770,30 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>23114</t>
-        </is>
-      </c>
+          <t>23229</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HopeTree Family Services — Richmond</t>
+          <t>Dermatology Associates of Virginia</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>hopetreefs.org</t>
+          <t>dermva.com</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bon Air</t>
+          <t>Reynolds Crossing</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10800 Midlothian Turnpike, Suite 300</t>
+          <t>6946 Forest Avenue, Suite 200</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6545,34 +6808,39 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>23235</t>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>804-285-2006</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Richmond Creative Counseling</t>
+          <t>Dermatology Associates of Virginia</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>richmondcreativecounseling.com</t>
+          <t>dermva.com</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>West End</t>
+          <t>Mechanicsville</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1900 Byrd Avenue</t>
+          <t>7498 Right Flank Road</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Mechanicsville</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6582,34 +6850,34 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>23230-3033</t>
+          <t>23116</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>804-592-6311</t>
+          <t>804-730-2652</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Richmond Creative Counseling</t>
+          <t>Dermatology Associates of Virginia</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>richmondcreativecounseling.com</t>
+          <t>dermva.com</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>West End</t>
+          <t>Bon Air</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1900 Byrd Ave</t>
+          <t>10800 Midlothian Turnpike, Suite 309</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -6624,34 +6892,39 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>23230</t>
+          <t>23235</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>804-794-2307</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Richmond Creative Counseling</t>
+          <t>Greater Richmond Partnership</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>richmondcreativecounseling.com</t>
+          <t>grpva.com</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>West End</t>
+          <t>Downtown</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8804 Patterson Ave</t>
+          <t>800 E. Canal Street</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Ste. 925 Richmond</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6661,34 +6934,35 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>23229</t>
-        </is>
-      </c>
+          <t>23219</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Chesterfield Auto Parts</t>
+          <t>Hanover Air</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>chesterfieldauto.com</t>
+          <t>hanoverair.com</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Southside / Midlothian corridor</t>
+          <t>Mechanicsville</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5111 Old Midlothian Turnpike</t>
+          <t>8162 Elm Drive</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Mechanicsville</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6698,39 +6972,35 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>23224</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>804-233-5481</t>
-        </is>
-      </c>
+          <t>23111</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Chesterfield Auto Parts</t>
+          <t>HopeTree Family Services — Richmond</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>chesterfieldauto.com</t>
+          <t>hopetreefs.org</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Bon Air</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>12910 Genito Road</t>
+          <t>10800 Midlothian Turnpike, Suite 300</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6740,39 +7010,35 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>23112</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>804-744-0716</t>
-        </is>
-      </c>
+          <t>23235</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Physical Therapy Solutions</t>
+          <t>Intercept Health</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>physicaltherapysolutions.net</t>
+          <t>intercepthealth.com</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mechanicsville</t>
+          <t>Richmond HQ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8201 Atlee Road</t>
+          <t>5511 Staples Mill Road, Suite 102</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Suite D Mechanicsville</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6782,34 +7048,39 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>23116</t>
+          <t>23228</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>804-440-3700</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Physical Therapy Solutions</t>
+          <t>Intercept Health</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>physicaltherapysolutions.net</t>
+          <t>intercepthealth.com</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Glen Allen</t>
+          <t>Roanoke HQ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4101 Cox Road</t>
+          <t>5673 Airport Road</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Suite 360 Glen Allen</t>
+          <t>Roanoke</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -6819,29 +7090,34 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>23060</t>
+          <t>24012</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>540-344-7700</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Physical Therapy Solutions</t>
+          <t>Interspan Staffing</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>physicaltherapysolutions.net</t>
+          <t>interspanstaffing.com</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Downtown</t>
+          <t>Eastern Chesterfield</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>407 East Canal Street</t>
+          <t>3908 Meadowdale Blvd</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -6856,34 +7132,35 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>23219</t>
-        </is>
-      </c>
+          <t>23234</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Byrd Property Management</t>
+          <t>James River Dermatology</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>byrdpm.com</t>
+          <t>jamesriverderm.com</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Mechanicsville</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2913 Fox Chase Ln</t>
+          <t>6372 Mechanicsville Turnpike, Suite 103</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Mechanicsville</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -6893,34 +7170,39 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>23112</t>
+          <t>23111</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>804-379-0116</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Byrd Property Management</t>
+          <t>James River Dermatology</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>byrdpm.com</t>
+          <t>jamesriverderm.com</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richmond city — verify neighborhood</t>
+          <t>Midlothian</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1127 W Main St</t>
+          <t>1316 Alverser Plaza</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Midlothian</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -6930,34 +7212,39 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>23220</t>
+          <t>23113</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>804-379-0116</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Byrd Property Management</t>
+          <t>Keyrenter Richmond</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>byrdpm.com</t>
+          <t>keyrenterrichmond.com</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Glen Allen</t>
+          <t>Libbie / Grove</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2400 Old Brick Rd, #178</t>
+          <t>6900 Patterson Ave</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Glen Allen</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -6967,34 +7254,35 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>23060</t>
-        </is>
-      </c>
+          <t>23226</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Byrd Property Management</t>
+          <t>KRS Holdings</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>byrdpm.com</t>
+          <t>krsholdings.com</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Libbie / Grove</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2913 Fox Chase Lane</t>
+          <t>2000 West Club Lane</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -7004,29 +7292,30 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>23112</t>
-        </is>
-      </c>
+          <t>23226</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Byrd Property Management</t>
+          <t>Lingo Staffing</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>byrdpm.com</t>
+          <t>lingostaffing.com</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Richmond city — verify neighborhood</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1127 W Main St</t>
+          <t>263 Wadsworth Drive</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -7041,34 +7330,39 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>23220</t>
+          <t>23236</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>804-594-6667</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Byrd Property Management</t>
+          <t>Lingo Staffing</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>byrdpm.com</t>
+          <t>lingostaffing.com</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Glen Allen</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2400 Old Brick Rd</t>
+          <t>263 Wadsworth Drive</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Glen Allen</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -7078,19 +7372,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>23060</t>
+          <t>23236</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>804-594-6667</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ProSafe Storage - Richmond</t>
+          <t>Love and Learn Child Care Center</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>prosafestorage.com</t>
+          <t>loveandlearnchildcarecenter.com</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -7100,7 +7399,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2100 Sheila Ln</t>
+          <t>5168 Nine Mile Road</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -7115,34 +7414,34 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>23225</t>
+          <t>23223</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(804) 292-2366</t>
+          <t>804-328-0444</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Premier HealthCare Associates</t>
+          <t>Love and Learn Child Care Center</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>premierhealthcare-va.com</t>
+          <t>loveandlearnchildcarecenter.com</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>West End</t>
+          <t>Richmond city — verify neighborhood</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>7702 E. Parham Road, Suite 101</t>
+          <t>5207 Nine Mile Rd</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -7157,34 +7456,30 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>23294</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>804-288-7901</t>
-        </is>
-      </c>
+          <t>23223</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Premier HealthCare Associates</t>
+          <t>Love and Learn Child Care Center</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>premierhealthcare-va.com</t>
+          <t>loveandlearnchildcarecenter.com</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>West End</t>
+          <t>Richmond city — verify neighborhood</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>7702 E. Parham Rd., Suite 101</t>
+          <t>5184 Nine Mile Rd</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -7199,39 +7494,35 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>23294</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>804-288-7901</t>
-        </is>
-      </c>
+          <t>23223</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>VitalCare Family Practice</t>
+          <t>Love and Learn Child Care Center</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>vitalcarefp.com</t>
+          <t>loveandlearnchildcarecenter.com</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Richmond city — verify neighborhood</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>7300 Ashlake Parkway, Suite 200</t>
+          <t>5168 Nine Mile Rd</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -7241,19 +7532,20 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>23832</t>
-        </is>
-      </c>
+          <t>23223</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>VitalCare Family Practice</t>
+          <t>Midlothian Mechanical</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>vitalcarefp.com</t>
+          <t>midlothianmechanical.com</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7263,12 +7555,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>7300 Ashlake Parkway, Suite 200</t>
+          <t>501 Research Rd</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>North Chesterfield</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -7278,39 +7570,35 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>23832</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>804-256-8282</t>
-        </is>
-      </c>
+          <t>23236</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>VitalCare Family Practice</t>
+          <t>Neurosurgical Associates</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>vitalcarefp.com</t>
+          <t>neurosurgicalva.com</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Short Pump</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>7300 Ashlake Parkway</t>
+          <t>1600 Wilkes Ridge Road, Suite 210</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Suite 200 Chesterfield</t>
+          <t>Henrico</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -7320,34 +7608,39 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>23832</t>
+          <t>23233</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>804-288-8204</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>VitalCare Family Practice</t>
+          <t>Neurosurgical Associates</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>vitalcarefp.com</t>
+          <t>neurosurgicalva.com</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>West End</t>
+          <t>Mechanicsville</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8006 Discovery Drive</t>
+          <t>8407 North Run Medical Drive</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Suite 400 Henrico</t>
+          <t>Mechanicsville</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -7357,34 +7650,39 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>23116</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>804-559-4880</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Advantage Primary Care</t>
+          <t>Neurosurgical Associates</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>advantagerva.com</t>
+          <t>neurosurgicalva.com</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>West End</t>
+          <t>Bon Air</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>7605 Forest Ave STE 412</t>
+          <t>1011 Johnston Willis Drive, Suite 100</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>North Chesterfield</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -7394,34 +7692,34 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>23235</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>804-381-6252</t>
+          <t>804-330-4990</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Advantage Primary Care</t>
+          <t>OrthoVirginia</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>advantagerva.com</t>
+          <t>orthovirginia.com</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>West End</t>
+          <t>Chippenham</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>7605 Forest Avenue, Suite 412</t>
+          <t>1115 Boulders Parkway, Suite 100</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -7436,39 +7734,39 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>23225</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>804-381-6252</t>
+          <t>804-320-1339</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Dominion Behavioral Healthcare - Richmond</t>
+          <t>OrthoVirginia</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>dbhrichmond.com</t>
+          <t>orthovirginia.com</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>West End</t>
+          <t>Henrico Parham</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2301 North Parham Rd</t>
+          <t>7650 East Parham Road, Suite 100</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Suite 5 Richmond</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -7478,29 +7776,34 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>23294</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>804-288-3136</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Virginia Veterinary Centers</t>
+          <t>OrthoVirginia</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>virginiaveterinarycenters.com</t>
+          <t>orthovirginia.com</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Richmond city — verify neighborhood</t>
+          <t>Shrader Road</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3312 West Cary St</t>
+          <t>7858 Shrader Road</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -7515,34 +7818,39 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>23294</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>804-270-1305</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Virginia Veterinary Centers</t>
+          <t>OrthoVirginia</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>virginiaveterinarycenters.com</t>
+          <t>orthovirginia.com</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>St. Mary's</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>12077 Hull Street Rd</t>
+          <t>5899 Bremo Road, Suite 100A</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -7552,34 +7860,39 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>23112</t>
+          <t>23226</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>804-288-8512</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Virginia Veterinary Centers</t>
+          <t>OrthoVirginia</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>virginiaveterinarycenters.com</t>
+          <t>orthovirginia.com</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Westchester</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1301 Central Park Blvd</t>
+          <t>15300 East West Road</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fredericksburg</t>
+          <t>Midlothian</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -7589,34 +7902,39 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>22401</t>
+          <t>23114</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>804-379-2414</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Virginia Veterinary Centers</t>
+          <t>OrthoVirginia</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>virginiaveterinarycenters.com</t>
+          <t>orthovirginia.com</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Short Pump</t>
+          <t>Westchester Ortho On Call</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4300 Greybull Drive</t>
+          <t>15564 Westchester Commons Way</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Henrico</t>
+          <t>Midlothian</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -7626,29 +7944,34 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>23233</t>
+          <t>23113</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>804-440-4878</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Virginia Veterinary Centers</t>
+          <t>OrthoVirginia</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>virginiaveterinarycenters.com</t>
+          <t>orthovirginia.com</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Hull St</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>12077 Hull Street Road</t>
+          <t>13212 Hull St. Rd</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -7664,33 +7987,38 @@
       <c r="G59" t="inlineStr">
         <is>
           <t>23112</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>804-419-9840</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AHG Construction &amp; Remodeling</t>
+          <t>Pediatric Associates of Richmond</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ahgva.com</t>
+          <t>parpeds.com</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mechanicsville</t>
+          <t>Short Pump</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>9600 Atlee Station Road</t>
+          <t>4300 Pouncey Tract Road</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mechanicsville</t>
+          <t>Glen Allen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -7700,39 +8028,39 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>23116</t>
+          <t>23060</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>804-299-3155</t>
+          <t>804-282-4205</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RVA Construction, Inc.</t>
+          <t>Pediatric Associates of Richmond</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>rvaconstruction.com</t>
+          <t>parpeds.com</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hanover / Ashland</t>
+          <t>West End</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>11206 Leadbetter Road, Suite 6</t>
+          <t>7240 Patterson Avenue, Suite 100</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ashland</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7742,39 +8070,39 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>23005</t>
+          <t>23229</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>804-622-5852</t>
+          <t>804-282-4205</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Dallan Construction</t>
+          <t>Pediatric Associates of Richmond</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>dallanconstruction.com</t>
+          <t>parpeds.com</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>West End</t>
+          <t>Mechanicsville</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>4900 Fitzhugh Avenue</t>
+          <t>8485 Bell Creek Road, Suite B3</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Mechanicsville</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7784,39 +8112,39 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>23230</t>
+          <t>23116</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>804-421-9326</t>
+          <t>804-282-4205</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Midlothian Mechanical</t>
+          <t>Pediatric Associates, PC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>midlothianmechanical.com</t>
+          <t>pediatricassociatespc.com</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Hioaks / Chippenham</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>501 Research Rd</t>
+          <t>1001 Hioaks Road</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>North Chesterfield</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7826,29 +8154,34 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>23236</t>
+          <t>23225</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>804-320-7139</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>W.G. Speeks</t>
+          <t>Pediatric Associates, PC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>wgspeeks.com</t>
+          <t>pediatricassociatespc.com</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Midlothian</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10711 Paulbrook Drive</t>
+          <t>13470 Tredegar Lake Parkway</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7868,34 +8201,34 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>804-276-2800</t>
+          <t>804-794-7788</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Triangle Plumbing Services</t>
+          <t>Pest Solutions</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>triangleplumbingservice.com</t>
+          <t>pestsolutionsva.com</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>West End</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3730A Hendricks Rd</t>
+          <t>5612 W Marshall St</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7905,34 +8238,35 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>23112</t>
-        </is>
-      </c>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Triangle Plumbing Services</t>
+          <t>Pest Solutions</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>triangleplumbingservice.com</t>
+          <t>pestsolutionsva.com</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>West End</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3730A Hendricks Rd</t>
+          <t>5612 W Marshall St</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7942,34 +8276,35 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>23112</t>
-        </is>
-      </c>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Triangle Plumbing Services</t>
+          <t>Physical Therapy Solutions</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>triangleplumbingservice.com</t>
+          <t>physicaltherapysolutions.net</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Mechanicsville</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>3730A Hendricks Rd</t>
+          <t>8201 Atlee Road</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Suite D Mechanicsville</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7979,34 +8314,35 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>23112</t>
-        </is>
-      </c>
+          <t>23116</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Triangle Plumbing Services</t>
+          <t>Physical Therapy Solutions</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>triangleplumbingservice.com</t>
+          <t>physicaltherapysolutions.net</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Glen Allen</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3730A Hendricks Rd</t>
+          <t>4101 Cox Road</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Midlothian</t>
+          <t>Suite 360 Glen Allen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -8016,34 +8352,35 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>23112</t>
-        </is>
-      </c>
+          <t>23060</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Hanover Air</t>
+          <t>Physical Therapy Solutions</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>hanoverair.com</t>
+          <t>physicaltherapysolutions.net</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mechanicsville</t>
+          <t>Downtown</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>8162 Elm Drive</t>
+          <t>407 East Canal Street</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mechanicsville</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -8053,19 +8390,20 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>23111</t>
-        </is>
-      </c>
+          <t>23219</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A Plus Roofing Company - Richmond VA</t>
+          <t>Premier HealthCare Associates</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>aplusroofing.com</t>
+          <t>premierhealthcare-va.com</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -8075,7 +8413,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2907 Hungary Spring Rd</t>
+          <t>7702 E. Parham Road, Suite 101</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -8090,19 +8428,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>23228</t>
+          <t>23294</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>804-288-7901</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A Plus Roofing Company - Richmond VA</t>
+          <t>Premier HealthCare Associates</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>aplusroofing.com</t>
+          <t>premierhealthcare-va.com</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8112,7 +8455,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2907 Hungary Spring Rd</t>
+          <t>7702 E. Parham Rd., Suite 101</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -8127,29 +8470,34 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>23228</t>
+          <t>23294</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>804-288-7901</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A Plus Roofing Company - Richmond VA</t>
+          <t>ProSafe Storage - Richmond</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>aplusroofing.com</t>
+          <t>prosafestorage.com</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>West End</t>
+          <t>Richmond city — verify neighborhood</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2907 Hungary Spring Rd</t>
+          <t>2100 Sheila Ln</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -8164,39 +8512,39 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>23228</t>
+          <t>23225</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(804) 752-0008</t>
+          <t>(804) 292-2366</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Pest Solutions</t>
+          <t>Relevate Property Guides</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>pestsolutionsva.com</t>
+          <t>relevatepg.com</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>West End</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>5612 W Marshall St</t>
+          <t>11207 Nuckols Rd, Suite F</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Glen Allen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8206,34 +8554,39 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>23230</t>
+          <t>23059</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>804-410-3300</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Pest Solutions</t>
+          <t>Relevate Property Guides</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>pestsolutionsva.com</t>
+          <t>relevatepg.com</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>West End</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>5612 W Marshall St</t>
+          <t>11207 Nuckols Rd Ste F</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Glen Allen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8243,29 +8596,30 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>23230</t>
-        </is>
-      </c>
+          <t>23059</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Keyrenter Richmond</t>
+          <t>Richmond Creative Counseling</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>keyrenterrichmond.com</t>
+          <t>richmondcreativecounseling.com</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Libbie / Grove</t>
+          <t>West End</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>6900 Patterson Ave</t>
+          <t>1900 Byrd Avenue</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -8280,34 +8634,39 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>23226</t>
+          <t>23230-3033</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>804-592-6311</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Relevate Property Guides</t>
+          <t>Richmond Creative Counseling</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>relevatepg.com</t>
+          <t>richmondcreativecounseling.com</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>West End</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>11207 Nuckols Rd, Suite F</t>
+          <t>1900 Byrd Ave</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Glen Allen</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8317,39 +8676,35 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>23059</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>804-410-3300</t>
-        </is>
-      </c>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Relevate Property Guides</t>
+          <t>Richmond Creative Counseling</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>relevatepg.com</t>
+          <t>richmondcreativecounseling.com</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>West End</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>11207 Nuckols Rd Ste F</t>
+          <t>8804 Patterson Ave</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Glen Allen</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8359,34 +8714,35 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>23059</t>
-        </is>
-      </c>
+          <t>23229</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>KRS Holdings</t>
+          <t>Richmond Gastroenterology Associates</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>krsholdings.com</t>
+          <t>richmondgastro.com</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Libbie / Grove</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2000 West Club Lane</t>
+          <t>169 Wadsworth Drive</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>N. Chesterfield</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8396,19 +8752,20 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>23226</t>
-        </is>
-      </c>
+          <t>23236</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Lingo Staffing</t>
+          <t>Richmond Gastroenterology Associates</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>lingostaffing.com</t>
+          <t>richmondgastro.com</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8418,12 +8775,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>263 Wadsworth Drive</t>
+          <t>223 Wadsworth Drive</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>N. Chesterfield</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -8436,36 +8793,32 @@
           <t>23236</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>804-594-6667</t>
-        </is>
-      </c>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Lingo Staffing</t>
+          <t>Richmond Gastroenterology Associates</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>lingostaffing.com</t>
+          <t>richmondgastro.com</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Short Pump</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>263 Wadsworth Drive</t>
+          <t>1600 Wilkes Ridge Drive Suite 200</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Henrico</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -8475,34 +8828,30 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>23236</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>804-594-6667</t>
-        </is>
-      </c>
+          <t>23233</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Interspan Staffing</t>
+          <t>Richmond Gastroenterology Associates</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>interspanstaffing.com</t>
+          <t>richmondgastro.com</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Eastern Chesterfield</t>
+          <t>West End</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>3908 Meadowdale Blvd</t>
+          <t>2369 Staples Mill Road Suite 100</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8517,34 +8866,35 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>23234</t>
-        </is>
-      </c>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TFA Logistics</t>
+          <t>Richmond Gastroenterology Associates</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>tfalogistics.com</t>
+          <t>richmondgastro.com</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Mechanicsville</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10448 Dow-Gil Road</t>
+          <t>8415 North Run Medical Drive</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ashland</t>
+          <t>Mechanicsville</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -8554,39 +8904,35 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>23005</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>804-798-1477</t>
-        </is>
-      </c>
+          <t>23116</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TFA Logistics</t>
+          <t>Richmond Gastroenterology Associates</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>tfalogistics.com</t>
+          <t>richmondgastro.com</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Short Pump</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>10448 Dow-Gil Rd</t>
+          <t>1600 Wilkes Ridge Drive Suite 100</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ashland</t>
+          <t>Henrico</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -8596,19 +8942,20 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>23005</t>
-        </is>
-      </c>
+          <t>23233</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TFA Logistics</t>
+          <t>Richmond Gastroenterology Associates</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>tfalogistics.com</t>
+          <t>richmondgastro.com</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -8618,12 +8965,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>10448 Dow-Gil Rd</t>
+          <t>15350 East West Road Suite 101</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ashland</t>
+          <t>Midlothian</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -8633,34 +8980,35 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>23005</t>
-        </is>
-      </c>
+          <t>23114</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Virginia Manufacturers Association</t>
+          <t>Richmond Nephrology Associates</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>vamanufacturers.com</t>
+          <t>richmondnephrologyassociates.com</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>West End</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2112 W. Laburnum Avenue</t>
+          <t>7001 West Broad Street, Suite A</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Suite 205 Richmond</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -8670,34 +9018,39 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>23227</t>
+          <t>23294</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>804-673-2722</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Greater Richmond Partnership</t>
+          <t>River Run Dental</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>grpva.com</t>
+          <t>riverrundentalspa.com</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Downtown</t>
+          <t>West End</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>800 E. Canal Street</t>
+          <t>7820 Shrader Road</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ste. 925 Richmond</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -8707,29 +9060,30 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>23219</t>
-        </is>
-      </c>
+          <t>23294</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Love and Learn Child Care Center</t>
+          <t>River Run Dental</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>loveandlearnchildcarecenter.com</t>
+          <t>riverrundentalspa.com</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Richmond city — verify neighborhood</t>
+          <t>West End</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>5168 Nine Mile Road</t>
+          <t>5001 Libbie Mill East Blvd. #125</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8744,39 +9098,35 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>23223</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>804-328-0444</t>
-        </is>
-      </c>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Love and Learn Child Care Center</t>
+          <t>River Run Dental</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>loveandlearnchildcarecenter.com</t>
+          <t>riverrundentalspa.com</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Richmond city — verify neighborhood</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>5207 Nine Mile Rd</t>
+          <t>14261 Winterview Parkway</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Midlothian</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -8786,34 +9136,35 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>23223</t>
-        </is>
-      </c>
+          <t>23113</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Love and Learn Child Care Center</t>
+          <t>River Run Dental</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>loveandlearnchildcarecenter.com</t>
+          <t>riverrundentalspa.com</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Richmond city — verify neighborhood</t>
+          <t>Short Pump</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>5184 Nine Mile Rd</t>
+          <t>3400 Haydenpark Lane Suite 203</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Henrico</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -8823,34 +9174,35 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>23223</t>
-        </is>
-      </c>
+          <t>23233</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Love and Learn Child Care Center</t>
+          <t>RVA Construction, Inc.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>loveandlearnchildcarecenter.com</t>
+          <t>rvaconstruction.com</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Richmond city — verify neighborhood</t>
+          <t>Hanover / Ashland</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>5168 Nine Mile Rd</t>
+          <t>11206 Leadbetter Road, Suite 6</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Ashland</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -8860,34 +9212,39 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>23223</t>
+          <t>23005</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>804-622-5852</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Blue and Gray Self-Storage</t>
+          <t>Sumser Insurance Professionals</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>blueandgraystorage.com</t>
+          <t>sumserinsurance.com</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Midlothian</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>15221 Hull Street Rd.</t>
+          <t>104 Walton Park Lane</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Midlothian</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -8897,7 +9254,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>23832</t>
+          <t>23114</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(804) 423-8372</t>
         </is>
       </c>
     </row>
@@ -8937,46 +9299,2633 @@
           <t>23114</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>(804) 423-8372</t>
-        </is>
-      </c>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sumser Insurance Professionals</t>
+          <t>TFA Logistics</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>sumserinsurance.com</t>
+          <t>tfalogistics.com</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>10448 Dow-Gil Road</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Ashland</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>23005</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>804-798-1477</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>TFA Logistics</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>tfalogistics.com</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>10448 Dow-Gil Rd</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Ashland</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>23005</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>TFA Logistics</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>tfalogistics.com</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>10448 Dow-Gil Rd</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Ashland</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>23005</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Triangle Plumbing Services</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>triangleplumbingservice.com</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
           <t>Midlothian</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>104 Walton Park Lane</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3730A Hendricks Rd</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
         <is>
           <t>Midlothian</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>23112</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Triangle Plumbing Services</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>triangleplumbingservice.com</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Midlothian</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3730A Hendricks Rd</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Midlothian</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>23112</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Triangle Plumbing Services</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>triangleplumbingservice.com</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Midlothian</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3730A Hendricks Rd</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Midlothian</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>23112</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Triangle Plumbing Services</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>triangleplumbingservice.com</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Midlothian</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3730A Hendricks Rd</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Midlothian</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>23112</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Virginia Urology</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>uro.com</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Stony Point Office</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>9101 Stony Point Drive</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>23235</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>804-330-9105</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Virginia Urology</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>uro.com</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Stony Point Surgery Center</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>9101 Stony Point Drive</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>23235</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>804-330-9105</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Virginia Urology</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>uro.com</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Hanover / Mechanicsville</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>8152 Pleasant Grove Road</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Mechanicsville</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>23116</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>804-330-9105</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Virginia Urology</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>uro.com</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Reynolds Crossing</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>6900 Forest Avenue, Suite 200</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>804-330-9105</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Virginia Urology</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>uro.com</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Far West End / Goochland</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>1700 Mills Road, Suite B</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Goochland</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>23233</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>804-330-9105</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Virginia Urology</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>uro.com</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>IR Center</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>1700 Mills Road, Suite A</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Goochland</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>23233</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>804-773-4700</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Virginia Urology</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>uro.com</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Prince George</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2025 Waterside Road, Suite 105</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Prince George</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>23875</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>804-330-9105</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Virginia Urology</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>uro.com</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Tappahannock</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>1396 B Tappahannock Blvd</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Tappahannock</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>22560</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>804-330-9105</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Virginia Urology</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>uro.com</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Emporia</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>6 Doctor's Drive</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Emporia</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>23847</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>804-330-9105</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Virginia Cardiovascular Specialists</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>vacardio.com</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Mechanicsville / Bell Creek</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>7515 Right Flank Road</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Mechanicsville</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>23116</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>804-559-0405</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Virginia Cardiovascular Specialists</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>vacardio.com</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Midlothian on Hull</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>6120 Harbourside Centre Loop</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Midlothian</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>23112</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>804-915-1400</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Virginia Cardiovascular Specialists</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>vacardio.com</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Prince George / Waterside</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>4700 Puddledock Road, Suite 400</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Prince George</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>23875</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>804-458-1740</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Virginia Cardiovascular Specialists</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>vacardio.com</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Quinton / New Kent</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>1850 Pocahontas Trail</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Quinton</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>23141</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>804-559-0405</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Virginia Cardiovascular Specialists</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>vacardio.com</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Richmond / Stony Point</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>8700 Stony Point Parkway, Suite 120</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>23235</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>804-323-5011</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Virginia Cardiovascular Specialists</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>vacardio.com</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Short Pump / West Creek</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>1630 Wilkes Ridge Parkway, Suite 303</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>23233</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>804-708-0445</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Virginia Cardiovascular Specialists</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>vacardio.com</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Tappahannock</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>1396 Tappahannock Blvd, Unit B</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Tappahannock</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>22560</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>804-288-4827</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Virginia Cardiovascular Specialists</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>vacardio.com</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Heart &amp; Vascular Surgery Center</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>8007 Discovery Drive, Unit B</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>23229</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>804-288-4827</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Virginia Cardiovascular Specialists</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>vacardio.com</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>West End / Forest Medical Plaza</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>7611 Forest Ave, Suite 100 &amp; 100A</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>23229</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>804-288-4827</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Virginia Family Dentistry</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>vadentist.com</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Atlee - Ashland</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>9484 Charter Gate Drive</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Ashland</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>23005</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>804-412-0599</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Virginia Family Dentistry</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>vadentist.com</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Brandermill - Woodlake</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>6510 Harbour View Court</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Midlothian</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>23112</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>804-739-6494</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Virginia Family Dentistry</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>vadentist.com</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Chester</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2601 Swiftrun Road</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Chester</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>23831</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>804-414-2550</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Virginia Family Dentistry</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>vadentist.com</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Huguenot Specialty Center</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>1801 Huguenot Road</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Midlothian</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>23113</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>804-419-1041</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Virginia Family Dentistry</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>vadentist.com</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ironbridge - Courthouse</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>6441 Ironbridge Road</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>23234</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>804-743-8189</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Virginia Family Dentistry</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>vadentist.com</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Mechanicsville Specialty Center</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>6000 Brashier Blvd</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Mechanicsville</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>23111</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>804-730-3457</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Virginia Family Dentistry</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>vadentist.com</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Midlothian - 288</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>14001 Charter Park Drive</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Midlothian</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
         <is>
           <t>23114</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>804-417-0245</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Virginia Family Dentistry</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>vadentist.com</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Powhatan</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2625 Anderson Highway</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Powhatan</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>23139</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>804-403-6036</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Virginia Family Dentistry</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>vadentist.com</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Tri-Cities</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>4710 Puddledock Road</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Prince George</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>23875</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>804-526-4886</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Virginia Family Dentistry</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>vadentist.com</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>West End Ortho &amp; Pediatric</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>12390 Three Chopt Road</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>23233</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>804-351-5432</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Virginia Eye Institute</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>vaeye.com</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Huguenot Bridge</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>400 Westhampton Station</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>23226</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>804-287-2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Virginia Eye Institute</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>vaeye.com</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Short Pump</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>12018 W. Broad St, Suite 100</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Henrico</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>23233</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>804-287-2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Virginia Eye Institute</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>vaeye.com</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Hanover</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>8120 Pleasant Grove Rd, Suite 100</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Mechanicsville</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>23116</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>804-287-2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Virginia Eye Institute</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>vaeye.com</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Reynolds Crossing</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>6946 Forest Avenue, Suite 100</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>804-287-2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Virginia Eye Institute</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>vaeye.com</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Puddledock</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2015 Waterside Road</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Prince George</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>23875</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>804-287-2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Virginia Eye Institute</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>vaeye.com</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Ironbridge</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>11601 Iron Bridge Road, Suite 104</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Chester</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>23831</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>804-287-2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Virginia Eye Institute</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>vaeye.com</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Westchester</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>611 Watkins Centre Pkwy, Building 2</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Midlothian</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>23114</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>804-287-2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Virginia Eye Institute</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>vaeye.com</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>The Aesthetic Center</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>12018 W. Broad Street, Suite 102</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Henrico</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>23233</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>804-287-2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Virginia Manufacturers Association</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>vamanufacturers.com</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2112 W. Laburnum Avenue</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Suite 205 Richmond</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>23227</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Vascular Surgery Associates</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>vascularsurgeryassociates.com</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>West End</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>7900 Shrader Road</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Henrico</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>23294</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>804-288-1953</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Vascular Surgery Associates</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>vascularsurgeryassociates.com</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Mechanicsville</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>8237 Meadowbridge Road</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Mechanicsville</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>23116</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>804-288-1953</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Vascular Surgery Associates</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>vascularsurgeryassociates.com</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Midlothian</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>13460 Tredegar Lake Parkway</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Midlothian</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>23112</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>804-288-1953</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Virginia Veterinary Centers</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>virginiaveterinarycenters.com</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Richmond city — verify neighborhood</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>3312 West Cary St</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>23221</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Virginia Veterinary Centers</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>virginiaveterinarycenters.com</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>12077 Hull Street Rd</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Midlothian</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>23112</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Virginia Veterinary Centers</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>virginiaveterinarycenters.com</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>1301 Central Park Blvd</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Fredericksburg</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>22401</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Virginia Veterinary Centers</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>virginiaveterinarycenters.com</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Short Pump</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>4300 Greybull Drive</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Henrico</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>23233</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Virginia Veterinary Centers</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>virginiaveterinarycenters.com</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>12077 Hull Street Road</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Midlothian</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>23112</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Virginia Women’s Center</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>virginiawomenscenter.com</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Central Business Office</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>7130 Glen Forest Drive, Suite 101</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>23226</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>804-288-4084</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Virginia Women’s Center</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>virginiawomenscenter.com</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>West End</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>6600 West Broad Street, Suite 100</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>804-288-4084</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Virginia Women’s Center</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>virginiawomenscenter.com</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Short Pump</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>12129 Graham Meadows Drive</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>23233</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>804-288-4084</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Virginia Women’s Center</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>virginiawomenscenter.com</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Midlothian</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>13801 St. Francis Boulevard, Suite 100</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Midlothian</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>23114</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>804-288-4084</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Virginia Women’s Center</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>virginiawomenscenter.com</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Mechanicsville</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>8364 Bell Creek Road</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Mechanicsville</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>23116</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>804-288-4084</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Virginia Women’s Center</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>virginiawomenscenter.com</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Kilmarnock</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>102 DMV Drive</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Kilmarnock</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>22482</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>804-288-4084</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>VitalCare Family Practice</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>vitalcarefp.com</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>7300 Ashlake Parkway, Suite 200</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>23832</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>VitalCare Family Practice</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>vitalcarefp.com</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>7300 Ashlake Parkway, Suite 200</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>23832</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>804-256-8282</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>VitalCare Family Practice</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>vitalcarefp.com</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>7300 Ashlake Parkway</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Suite 200 Chesterfield</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>23832</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>VitalCare Family Practice</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>vitalcarefp.com</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>West End</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>8006 Discovery Drive</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Suite 400 Henrico</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>23229</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Virginia Physicians for Women</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>vpfw.com</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>13801 St. Francis Boulevard, Suite 150</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Midlothian</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>23114</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(804) 897-2100</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>W.G. Speeks</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>wgspeeks.com</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>10711 Paulbrook Drive</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Midlothian</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>23112</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>804-276-2800</t>
         </is>
       </c>
     </row>
